--- a/data/output/2025/evaluasi_33.xlsx
+++ b/data/output/2025/evaluasi_33.xlsx
@@ -41,6 +41,8 @@
     <sheet name="3376" sheetId="32" state="visible" r:id="rId32"/>
     <sheet name="3323" sheetId="33" state="visible" r:id="rId33"/>
     <sheet name="3373" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="3328" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="3372" sheetId="36" state="visible" r:id="rId36"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1372,7 +1374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1488,6 +1490,90 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3318</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Pati</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.5098284682239375</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3318</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Pati</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3318</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Pati</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.08187216016117596</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1618,6 +1704,118 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3316</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Blora</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>48.16988837578689</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3316</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Blora</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3316</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Blora</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.08188216390285916</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3316</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Blora</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8160064761922323</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1762,18 +1960,102 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>-1.729733100382097</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3317</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Rembang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3317</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Rembang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.7824915237166927</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3317</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Rembang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>-2.485761006512857</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>sog_q_pi_q4-25</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -1790,7 +2072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1934,6 +2216,118 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3301</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Cilacap</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>29.30175256791248</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3301</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Cilacap</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3301</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Cilacap</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.328672708533374</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3301</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Cilacap</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.5804549530902684</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1948,7 +2342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2134,18 +2528,130 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>85.86921527268288</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3325</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Batang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3325</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Batang</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>18.53542171744706</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3325</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Batang</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8017161919286994</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3325</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Batang</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>-2.112104068869095</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -2162,7 +2668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2306,6 +2812,174 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3306</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Purworejo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>8.230058697635359</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3306</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Purworejo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>19.80305609420703</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3306</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Purworejo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3306</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Purworejo</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.5668943026405854</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3306</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Purworejo</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.76472948194196</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3306</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Purworejo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.887959197442694</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2548,6 +3222,146 @@
       <c r="F8" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3374</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Semarang</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.1632056636388654</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3374</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Semarang</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>52.24346526950259</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3374</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Semarang</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3374</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Semarang</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4.029906505013934</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3374</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Semarang</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.4934628076466712</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2562,7 +3376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2874,6 +3688,286 @@
       <c r="F11" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3311</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukoharjo</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>8.053523983732825</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3311</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukoharjo</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4.816322437274147</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3311</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukoharjo</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>7.30097536265394</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3311</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukoharjo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>48.24544215636641</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3311</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukoharjo</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>9.193444158199398</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3311</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukoharjo</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3311</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukoharjo</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-4.046041162135509</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3311</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukoharjo</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-13.55962024989949</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>3311</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukoharjo</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.8518349881993477</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>3311</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukoharjo</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.4097415998589353</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2888,7 +3982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2976,6 +4070,90 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3321</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Demak</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>67.96907136885181</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3321</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Demak</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3321</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Demak</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2028236324665892</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2990,7 +4168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3050,6 +4228,202 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3302</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Banyumas</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.987171466015083</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3302</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Banyumas</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>14.2200422852543</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3302</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Banyumas</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3302</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Banyumas</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>21.1545040465896</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3302</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Banyumas</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>15.81803801932947</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3302</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Banyumas</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.8355109282493846</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3302</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Banyumas</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.3250476532006618</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3064,7 +4438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3208,6 +4582,202 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3313</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Karanganyar</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-4.526738085145056</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3313</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Karanganyar</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.02275452517091791</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3313</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Karanganyar</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>82.51600435668011</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3313</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Karanganyar</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3313</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Karanganyar</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>19.33906831312721</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3313</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Karanganyar</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>7.424626192864679</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3313</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Karanganyar</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.7923709952819726</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3222,7 +4792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3618,6 +5188,258 @@
       <c r="F14" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3303</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Purbalingga</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4.878616272424407</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3303</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Purbalingga</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>67.23716037354447</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3303</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Purbalingga</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3303</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Purbalingga</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>34.81701621661318</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3303</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Purbalingga</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-5.172660016137512</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>3303</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Purbalingga</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.817468569967541</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>3303</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Purbalingga</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-4.002448700470918</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>3303</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Purbalingga</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-5.159085695438281</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3303</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Purbalingga</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.5145771133916043</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3632,7 +5454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3748,6 +5570,174 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3304</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Banjarnegara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>14.09924493219687</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3304</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Banjarnegara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3304</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Banjarnegara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8.491894635219749</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3304</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Banjarnegara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-14.04583020645134</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3304</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Banjarnegara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.6487404126770261</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3304</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Banjarnegara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-13.2139155501346</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3762,7 +5752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3822,6 +5812,146 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3305</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kebumen</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5.748266790730573</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3305</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kebumen</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>54.67823409867923</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3305</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kebumen</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3305</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kebumen</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>13.74828183320235</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3305</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kebumen</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.8544027695429143</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3836,7 +5966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3924,6 +6054,146 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3307</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Wonosobo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5.215925375386447</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3307</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Wonosobo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>37.85558940625132</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3307</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Wonosobo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3307</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Wonosobo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.55192750085278</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3307</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Wonosobo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1860749715460983</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3938,7 +6208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4138,6 +6408,118 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3308</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Magelang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3308</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Magelang</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>15.27328973037136</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3308</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Magelang</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7.54591505406597</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3308</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Magelang</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.6876131409636231</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -4152,7 +6534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4212,6 +6594,90 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3309</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Boyolali</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>42.00297503214281</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3309</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Boyolali</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3309</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Boyolali</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.8547408273978815</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -4226,7 +6692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4286,6 +6752,174 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3310</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Klaten</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5.326474763323289</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3310</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Klaten</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>51.40141680344436</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3310</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Klaten</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3310</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Klaten</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.02799957180186298</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3310</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Klaten</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.375650875602912</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3310</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Klaten</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8585068765085443</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -4300,7 +6934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4486,20 +7120,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2.710902953463763</v>
+        <v>75.20269934782313</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pi_q4-25</t>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -4514,18 +7148,130 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3315</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Grobogan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2.506092111705412</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3315</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Grobogan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8006487245337032</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3315</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Grobogan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.710902953463763</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3315</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Grobogan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>-2.079898489191395</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -4542,7 +7288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4630,6 +7376,118 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3319</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kudus</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.545567596169296</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3319</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kudus</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>66.13550399950856</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3319</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kudus</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3319</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kudus</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.835691962543451</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -4644,7 +7502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4746,18 +7604,158 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D4" t="n">
+        <v>71.01453911933633</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3320</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Jepara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3320</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Jepara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>27.37576643044969</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3320</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Jepara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8.356580323592469</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3320</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Jepara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6968722522747091</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3320</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Jepara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>2.775765655323888</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -4774,7 +7772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5002,6 +8000,118 @@
       <c r="F8" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3314</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Sragen</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.06167837343836467</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3314</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Sragen</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>43.48200129147537</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3314</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Sragen</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3314</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Sragen</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1243905178693298</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -5016,7 +8126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5076,6 +8186,174 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3322</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Semarang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>35.46639444071261</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3322</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Semarang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3322</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Semarang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3.604646395039738</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3322</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Semarang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-8.384768056031101</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3322</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Semarang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-6.593524609335828</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3322</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Semarang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.7010983119769993</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -5090,7 +8368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5220,18 +8498,102 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3329</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Brebes</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2.806532078214921</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3329</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Brebes</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.662476003246171</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3329</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Brebes</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>-5.113444157294535</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>sog_q_pi_q4-25</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -5248,7 +8610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5336,6 +8698,146 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3376</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Tegal</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.611611886945943</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3376</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Tegal</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>46.57361091401416</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3376</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Tegal</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3376</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Tegal</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10.73106611247889</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3376</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Tegal</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8350652862020737</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -5350,7 +8852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5410,6 +8912,118 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3323</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Temanggung</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>71.34876578758221</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3323</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Temanggung</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3323</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Temanggung</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3.744397153673641</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3323</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Temanggung</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3388482181421513</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -5424,7 +9038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5484,6 +9098,546 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3373</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Salatiga</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-3.132066924878805</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3373</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Salatiga</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>40.2173409971987</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3373</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Salatiga</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3373</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Salatiga</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>10.44917911229297</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3373</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Salatiga</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.7694908577242348</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3328</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Tegal</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.9010942117812688</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3328</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Tegal</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>55.4038347638439</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3328</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Tegal</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3328</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Tegal</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11.57106615432911</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3328</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Tegal</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.6345704289562911</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3372</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Surakarta</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3372</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Surakarta</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>13.03326079088588</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3372</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Surakarta</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9737356468570721</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3372</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Surakarta</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10.79108437006074</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3372</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Surakarta</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.6569356640165662</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3372</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Surakarta</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.7326278848873904</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -5498,7 +9652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5558,6 +9712,174 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3327</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Pemalang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-5.360128358660627</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3327</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Pemalang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>40.42532462996345</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3327</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Pemalang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7.204405800749508</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3327</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Pemalang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3327</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Pemalang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.5675147710095</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3327</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Pemalang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10.79531578381116</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -5572,7 +9894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5842,20 +10164,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-15950.97263020591</v>
+        <v>57.19785335629538</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>sog_q_pi_q4-25</t>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -5870,20 +10192,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-16707.43348596982</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pi_q4-25</t>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -5898,18 +10220,102 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>0.6431042191796321</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3312</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Wonogiri</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-15950.97263020591</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3312</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Wonogiri</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-16707.43348596982</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3312</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Wonogiri</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>-4220.27844830189</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -5926,7 +10332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6070,6 +10476,174 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3324</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kendal</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.963860794042829</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3324</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kendal</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>48.65016967741788</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3324</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kendal</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3324</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kendal</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-2.733796202548712</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3324</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kendal</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.357279575176157</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3324</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kendal</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.7857702846564143</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -6084,7 +10658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6410,18 +10984,102 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>71.69301725449733</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3326</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Pekalongan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3326</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Pekalongan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.8051802204972369</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3326</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Pekalongan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>2.980296858852501</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -6438,7 +11096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6554,6 +11212,90 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3371</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Magelang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-3.132998755188095</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3371</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Magelang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3371</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Magelang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.7135663014668017</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -6568,7 +11310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6715,6 +11457,90 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3375</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Pekalongan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3375</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Pekalongan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.7920009449025376</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3375</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Pekalongan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.7619590778756188</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
